--- a/AI Audit Log_DangThanhTung.xlsx
+++ b/AI Audit Log_DangThanhTung.xlsx
@@ -4,18 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Week1" sheetId="2" r:id="rId2"/>
-    <sheet name="Week2" sheetId="3" r:id="rId3"/>
-    <sheet name="Week3" sheetId="4" r:id="rId4"/>
-    <sheet name="Week4" sheetId="5" r:id="rId5"/>
-    <sheet name="Week5" sheetId="6" r:id="rId6"/>
-    <sheet name="Week6" sheetId="7" r:id="rId7"/>
-    <sheet name="Week7" sheetId="8" r:id="rId8"/>
-    <sheet name="Week8" sheetId="9" r:id="rId9"/>
+    <sheet name="Week2" sheetId="2" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" r:id="rId5"/>
+    <sheet name="Week6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week7" sheetId="7" r:id="rId7"/>
+    <sheet name="Week8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="71">
   <si>
     <t>STT</t>
   </si>
@@ -174,6 +173,81 @@
   </si>
   <si>
     <t>AI đề xuất tách frontend, backend, database, testing. Sau khi đánh giá, quyết định phân chia theo năng lực thực tế từng thành viên thay vì chia đều, giúp tối ưu tốc độ hoàn thành và giảm conflict khi merge code.</t>
+  </si>
+  <si>
+    <t>Giai đoạn</t>
+  </si>
+  <si>
+    <t>Nội dung</t>
+  </si>
+  <si>
+    <t>Phản hồi AI</t>
+  </si>
+  <si>
+    <t>Phản hồi Con người</t>
+  </si>
+  <si>
+    <t>Khác biệt</t>
+  </si>
+  <si>
+    <t>Sequence Diagram</t>
+  </si>
+  <si>
+    <t>Vẽ diagram Car Return process</t>
+  </si>
+  <si>
+    <t>Vẽ đúng UML, đủ các actor như BookingController, BookingService, CarRepository, BookingRepository, PaymentService. Tuy nhiên vẫn tập trung vào luồng chính nên chưa xử lý tốt các tình huống phát sinh như thanh toán thất bại hay tranh chấp khi xác nhận booking.</t>
+  </si>
+  <si>
+    <t>Bổ sung đầy đủ các nhánh xử lý như thanh toán thành công / thất bại, thêm cơ chế retry khi cần và xử lý khóa giao dịch khi có nhiều request đồng thời. Ngoài ra còn tính luôn các case như timeout hoặc lỗi inventory.</t>
+  </si>
+  <si>
+    <t>AI đi nhanh theo luồng chính nên gọn nhưng thiếu chiều sâu. Con người làm chậm hơn nhưng bao quát được các tình huống thực tế và tính ổn định hệ thống.</t>
+  </si>
+  <si>
+    <t>Activity Diagram</t>
+  </si>
+  <si>
+    <t>Vẽ Car Return + Inspection + Fee Calculation</t>
+  </si>
+  <si>
+    <t>Trình bày các bước rõ ràng theo trình tự, có decision cho việc phát sinh phí. Tuy nhiên các bước bị xếp tuần tự nên chưa tối ưu, thiếu điều kiện ràng buộc và chưa phản ánh đúng logic nghiệp vụ thực tế.</t>
+  </si>
+  <si>
+    <t>Tách các bước có thể chạy song song như kiểm tra xe và tính phí, thêm điều kiện ràng buộc rõ ràng, đồng thời bổ sung luồng xử lý khi xe bị hư hỏng dẫn đến cập nhật trạng thái không khả dụng.</t>
+  </si>
+  <si>
+    <t>AI tập trung vào flow dễ hiểu, còn con người tối ưu lại quy trình để sát thực tế hơn và cải thiện hiệu suất xử lý.</t>
+  </si>
+  <si>
+    <t>Class Diagram</t>
+  </si>
+  <si>
+    <t>Tạo class cho User, Staff, Customer, Booking, Car, Payment, Repositories</t>
+  </si>
+  <si>
+    <t>Định nghĩa đúng các entity cơ bản nhưng còn đơn giản, dùng kiểu dữ liệu chung chung như String cho status, thiếu constraint cho amount và chưa rõ quan hệ giữa các class. Một số hàm nghiệp vụ quan trọng cũng chưa được thể hiện.</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa lại bằng enum cho status, thêm ràng buộc dữ liệu rõ ràng, làm rõ quan hệ 1-n giữa Customer và Booking, đồng thời bổ sung các method nghiệp vụ như tính phí trễ, kiểm tra khả dụng xe và hoàn tiền.</t>
+  </si>
+  <si>
+    <t>AI thiên về khung tổng quát, Con người đi sâu vào business logic và thiết kế chặt chẽ hơn.</t>
+  </si>
+  <si>
+    <t>Design Quality</t>
+  </si>
+  <si>
+    <t>So sánh tổng thể AI vs Con người</t>
+  </si>
+  <si>
+    <t>Tổng thể đúng chuẩn UML, dựng nhanh và rõ ràng, phù hợp để phác thảo ban đầu. Tuy nhiên còn thiếu ngữ cảnh nghiệp vụ, chưa xử lý hết edge case và chưa tối ưu hiệu suất hệ thống.</t>
+  </si>
+  <si>
+    <t>Thiết kế đầy đủ hơn với logic nghiệp vụ rõ ràng, xử lý tốt các tình huống lỗi, tối ưu luồng xử lý song song và bao quát các trường hợp đặc biệt như timeout hay hư hỏng xe.</t>
+  </si>
+  <si>
+    <t>AI mạnh ở tốc độ và khung ban đầu, Con người mạnh ở chiều sâu thiết kế, tính thực tế và độ hoàn thiện hệ thống.</t>
   </si>
   <si>
     <t>W</t>
@@ -828,12 +902,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -850,9 +936,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1203,73 +1286,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" ht="71.25" spans="1:4">
-      <c r="A2" s="5">
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" ht="57" spans="1:4">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="57" spans="1:4">
-      <c r="A3" s="5">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" ht="71.25" spans="1:4">
-      <c r="A4" s="5">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="85.5" spans="1:4">
-      <c r="A5" s="5">
+    <row r="5" ht="71.25" spans="1:4">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1291,128 +1374,128 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="71.25" spans="1:4">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="57" spans="1:4">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="57" spans="1:4">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="42.75" spans="1:4">
+      <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="57" spans="1:4">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="42.75" spans="1:4">
+      <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" ht="57" spans="1:4">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="42.75" spans="1:4">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" ht="42.75" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" ht="42.75" spans="1:4">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="28.5" spans="1:4">
+      <c r="A7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="42.75" spans="1:4">
-      <c r="A8" s="2" t="s">
+    <row r="8" ht="28.5" spans="1:4">
+      <c r="A8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" ht="42.75" spans="1:4">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="28.5" spans="1:4">
+      <c r="A9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1425,9 +1508,118 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="57.375" customWidth="1"/>
+    <col min="5" max="5" width="47" customWidth="1"/>
+    <col min="6" max="6" width="54.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" ht="57" spans="1:6">
+      <c r="A2" s="2">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" ht="57" spans="1:6">
+      <c r="A3" s="2">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25" spans="1:6">
+      <c r="A4" s="2">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" ht="57" spans="1:6">
+      <c r="A5" s="2">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1452,7 +1644,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1492,15 +1684,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/AI Audit Log_DangThanhTung.xlsx
+++ b/AI Audit Log_DangThanhTung.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885"/>
+    <workbookView windowWidth="28800" windowHeight="12885" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
   <si>
     <t>STT</t>
   </si>
@@ -251,6 +251,90 @@
   </si>
   <si>
     <t>W</t>
+  </si>
+  <si>
+    <t>Giai đoạn / Thành phần DTC</t>
+  </si>
+  <si>
+    <t>Tôi cần xây dựng ứng dụng Todo List bằng React Native có chức năng đăng nhập và quản lý công việc. Hãy liệt kê các entity và thuộc tính cần thiết.</t>
+  </si>
+  <si>
+    <t>AI đề xuất các entity User, Task và LoginSession cùng nhiều thuộc tính khác nhau. Sau khi phân tích yêu cầu đề bài, tôi chỉ giữ lại các thuộc tính cần thiết gồm username, password cho User và id, title, completed cho Task. Các thuộc tính như email, avatar và createdDate được loại bỏ vì không phục vụ chức năng của ứng dụng.</t>
+  </si>
+  <si>
+    <t>Hãy phân tích ứng dụng Todo List thành các màn hình và chức năng nhỏ.</t>
+  </si>
+  <si>
+    <t>AI đề xuất chia hệ thống thành Login Screen, Main Screen, Database Layer và Navigation Layer. Tôi chấp nhận cấu trúc này và triển khai thành các module riêng để tăng khả năng bảo trì và tái sử dụng mã nguồn.</t>
+  </si>
+  <si>
+    <t>Cho tôi ví dụ các ứng dụng React Native sử dụng React Navigation và SQLite.</t>
+  </si>
+  <si>
+    <t>AI cung cấp một số mô hình ứng dụng phổ biến. Sau khi tham khảo, tôi nhận thấy đề bài chỉ yêu cầu luồng Login → Main Screen nên đã đơn giản hóa thiết kế để phù hợp với phạm vi dự án.</t>
+  </si>
+  <si>
+    <t>Algorithm Design</t>
+  </si>
+  <si>
+    <t>Viết thuật toán thêm, xóa và cập nhật trạng thái hoàn thành của Task.</t>
+  </si>
+  <si>
+    <t>AI tạo pseudo code cho các chức năng CRUD. Tôi kiểm tra lại và bổ sung bước kiểm tra dữ liệu đầu vào nhằm ngăn việc thêm các công việc có tiêu đề rỗng.</t>
+  </si>
+  <si>
+    <t>Database Design</t>
+  </si>
+  <si>
+    <t>Thiết kế cơ sở dữ liệu SQLite cho ứng dụng Todo List.</t>
+  </si>
+  <si>
+    <t>AI đề xuất bảng Tasks gồm các trường id, title và completed. Tôi sử dụng thiết kế này vì đáp ứng đầy đủ yêu cầu lưu trữ danh sách công việc của đề bài mà không tạo dữ liệu dư thừa.</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Viết mã React Native sử dụng SQLite để thêm và hiển thị danh sách Task.</t>
+  </si>
+  <si>
+    <t>AI cung cấp đoạn mã mẫu. Trong quá trình thử nghiệm, tôi phát hiện một số trường hợp lỗi truy vấn cơ sở dữ liệu chưa được xử lý. Tôi đã bổ sung try-catch và thông báo lỗi phù hợp.</t>
+  </si>
+  <si>
+    <t>State Management</t>
+  </si>
+  <si>
+    <t>Làm thế nào để đồng bộ dữ liệu SQLite với FlatList trong React Native?</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng useState kết hợp hàm loadTasks() sau mỗi thao tác CRUD. Tôi áp dụng giải pháp này để đảm bảo giao diện luôn hiển thị dữ liệu mới nhất từ cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>AsyncStorage</t>
+  </si>
+  <si>
+    <t>Viết chức năng Remember Password bằng AsyncStorage.</t>
+  </si>
+  <si>
+    <t>AI cung cấp ví dụ lưu username và password bằng AsyncStorage. Tôi điều chỉnh cách lưu dữ liệu sang định dạng JSON và bổ sung bước kiểm tra dữ liệu tồn tại trước khi thực hiện đăng nhập tự động.</t>
+  </si>
+  <si>
+    <t>Testing &amp; Debugging</t>
+  </si>
+  <si>
+    <t>Kiểm tra các trường hợp lỗi có thể xảy ra trong ứng dụng Todo List.</t>
+  </si>
+  <si>
+    <t>AI liệt kê các trường hợp như đăng nhập thiếu thông tin, task rỗng, lỗi kết nối cơ sở dữ liệu và lỗi đọc dữ liệu từ AsyncStorage. Tôi sử dụng danh sách này làm checklist để kiểm thử ứng dụng.</t>
+  </si>
+  <si>
+    <t>Reflection</t>
+  </si>
+  <si>
+    <t>Đánh giá ưu điểm và hạn chế của giải pháp hiện tại.</t>
+  </si>
+  <si>
+    <t>AI nhận xét SQLite phù hợp với ứng dụng nhỏ nhưng không hỗ trợ đồng bộ dữ liệu trực tuyến như Firebase. Sau khi xem xét yêu cầu đề bài, tôi quyết định tiếp tục sử dụng SQLite vì đáp ứng đầy đủ chức năng bắt buộc và dễ triển khai hơn.</t>
   </si>
 </sst>
 </file>
@@ -908,6 +992,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -916,9 +1006,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -933,9 +1020,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1286,73 +1370,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:5">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" ht="57" spans="1:4">
-      <c r="A2" s="9">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="57" spans="1:4">
-      <c r="A3" s="9">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" ht="71.25" spans="1:4">
-      <c r="A4" s="9">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="71.25" spans="1:4">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1374,128 +1458,128 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="57" spans="1:4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" ht="42.75" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" ht="42.75" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" ht="42.75" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="28.5" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" ht="28.5" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" ht="28.5" spans="1:4">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1520,102 +1604,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" ht="57" spans="1:6">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" ht="57" spans="1:6">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" ht="71.25" spans="1:6">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" ht="57" spans="1:6">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1656,9 +1740,170 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="3" max="3" width="85.875" customWidth="1"/>
+    <col min="4" max="4" width="72.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="57" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" ht="42.75" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" ht="42.75" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:4">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" ht="42.75" spans="1:4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" ht="42.75" spans="1:4">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:4">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75" spans="1:4">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75" spans="1:4">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75" spans="1:4">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
